--- a/data/SO.xlsx
+++ b/data/SO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2025-27 PGDM 2nd Year\Ravinder sir\2025-27 TERM 5\Attendance sheet of term-5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sritam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B653B8-A26E-4A5A-8F76-4B7F5512CEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA716FB1-300E-41FF-BD31-0934C1A25DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{08DE5EE7-203A-4E69-9FD6-C456FB6D5E37}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{08DE5EE7-203A-4E69-9FD6-C456FB6D5E37}"/>
   </bookViews>
   <sheets>
     <sheet name="A" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="404">
   <si>
     <t>Roll No</t>
   </si>
@@ -1250,13 +1247,19 @@
   </si>
   <si>
     <t>pgdm25chaitanya_s@mdi.ac.in</t>
+  </si>
+  <si>
+    <t>25P055</t>
+  </si>
+  <si>
+    <t>Sritam Tripathy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1275,6 +1278,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1683,14 +1692,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A45922-84FA-4445-9780-5923E5720D1B}">
-  <dimension ref="A1:C66"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C67"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>244</v>
       </c>
@@ -1701,7 +1710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1712,7 +1721,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <f>A2+1</f>
         <v>2</v>
@@ -1724,9 +1733,9 @@
         <v>252</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <f t="shared" ref="A4:A66" si="0">A3+1</f>
+        <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1736,7 +1745,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1748,7 +1757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1760,7 +1769,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1772,7 +1781,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1784,7 +1793,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1796,7 +1805,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1808,7 +1817,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1820,7 +1829,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1832,7 +1841,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1844,7 +1853,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1856,7 +1865,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1868,7 +1877,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1880,7 +1889,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1892,7 +1901,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1904,7 +1913,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1916,7 +1925,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1928,7 +1937,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1940,7 +1949,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1952,7 +1961,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1964,7 +1973,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1976,7 +1985,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1988,7 +1997,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2000,7 +2009,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2012,7 +2021,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2024,7 +2033,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2036,7 +2045,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2048,7 +2057,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2060,7 +2069,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2072,7 +2081,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2084,7 +2093,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2096,7 +2105,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2108,7 +2117,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2120,7 +2129,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2132,7 +2141,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -2144,7 +2153,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -2156,7 +2165,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -2168,7 +2177,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -2180,7 +2189,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -2192,7 +2201,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -2204,7 +2213,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -2216,7 +2225,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -2228,7 +2237,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -2240,7 +2249,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -2252,7 +2261,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -2264,7 +2273,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -2276,7 +2285,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -2288,7 +2297,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -2300,7 +2309,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -2312,7 +2321,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -2324,7 +2333,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -2336,7 +2345,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -2348,7 +2357,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -2360,7 +2369,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -2372,7 +2381,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -2384,7 +2393,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -2396,7 +2405,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -2408,7 +2417,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -2420,7 +2429,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -2432,7 +2441,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -2444,7 +2453,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -2456,7 +2465,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -2468,7 +2477,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -2478,6 +2487,18 @@
       </c>
       <c r="C66" s="1" t="s">
         <v>185</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" s="2">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -2486,6 +2507,7 @@
       <sortCondition ref="B1:B66"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2493,13 +2515,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F17176-46CF-4EE7-BC42-8A450C963F8F}">
   <dimension ref="A1:C68"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>244</v>
       </c>
@@ -2510,7 +2532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2521,7 +2543,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <f>A2+1</f>
         <v>2</v>
@@ -2533,7 +2555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -2545,7 +2567,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2557,7 +2579,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2569,7 +2591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2581,7 +2603,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2593,7 +2615,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2605,7 +2627,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2617,7 +2639,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2629,7 +2651,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2641,7 +2663,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2653,7 +2675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2665,7 +2687,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2677,7 +2699,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2689,7 +2711,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2701,7 +2723,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2713,7 +2735,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2725,7 +2747,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2737,7 +2759,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2749,7 +2771,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2761,7 +2783,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2773,7 +2795,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2785,7 +2807,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2797,7 +2819,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2809,7 +2831,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2821,7 +2843,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2833,7 +2855,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2845,7 +2867,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2857,7 +2879,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2869,7 +2891,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2881,7 +2903,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2893,7 +2915,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2905,7 +2927,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2917,7 +2939,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2929,7 +2951,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2941,7 +2963,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -2953,7 +2975,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -2965,7 +2987,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -2977,7 +2999,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -2989,7 +3011,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -3001,7 +3023,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -3013,7 +3035,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -3025,7 +3047,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -3037,7 +3059,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3049,7 +3071,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3061,7 +3083,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3073,7 +3095,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -3085,7 +3107,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3097,7 +3119,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -3109,7 +3131,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -3121,7 +3143,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -3133,7 +3155,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -3145,7 +3167,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -3157,7 +3179,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -3169,7 +3191,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -3181,7 +3203,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -3193,7 +3215,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -3205,7 +3227,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -3217,7 +3239,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -3229,7 +3251,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -3241,7 +3263,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -3253,7 +3275,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -3265,7 +3287,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -3277,7 +3299,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -3289,7 +3311,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -3301,7 +3323,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <f t="shared" ref="A68" si="1">A67+1</f>
         <v>67</v>
@@ -3319,11 +3341,11 @@
       <sortCondition ref="B1:B68"/>
     </sortState>
   </autoFilter>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3332,15 +3354,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A18B3877-6DE7-40F0-94FF-6C8109170F2F}">
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.453125" customWidth="1"/>
+    <col min="5" max="5" width="25.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>244</v>
       </c>
@@ -3357,7 +3379,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -3374,7 +3396,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -3391,7 +3413,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3408,7 +3430,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3425,7 +3447,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3442,7 +3464,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -3459,7 +3481,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -3476,7 +3498,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -3493,7 +3515,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -3510,7 +3532,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -3527,7 +3549,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -3544,7 +3566,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -3561,7 +3583,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -3578,7 +3600,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -3595,7 +3617,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -3612,7 +3634,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -3629,7 +3651,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -3646,7 +3668,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -3663,7 +3685,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -3680,7 +3702,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -3697,7 +3719,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -3714,7 +3736,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -3731,7 +3753,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -3748,7 +3770,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -3765,7 +3787,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -3782,7 +3804,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -3799,7 +3821,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -3816,7 +3838,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -3833,7 +3855,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -3850,7 +3872,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -3867,7 +3889,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -3884,7 +3906,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -3901,7 +3923,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -3918,7 +3940,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -3935,7 +3957,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -3952,7 +3974,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -3969,7 +3991,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -3986,7 +4008,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -4003,7 +4025,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -4020,7 +4042,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -4037,7 +4059,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -4054,7 +4076,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -4071,7 +4093,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -4088,7 +4110,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -4105,7 +4127,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -4122,7 +4144,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -4139,7 +4161,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -4156,7 +4178,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -4173,7 +4195,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -4190,7 +4212,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -4207,7 +4229,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -4224,7 +4246,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -4241,7 +4263,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -4258,7 +4280,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -4275,7 +4297,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -4292,7 +4314,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -4309,7 +4331,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -4326,7 +4348,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -4343,7 +4365,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -4360,7 +4382,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -4377,7 +4399,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -4394,7 +4416,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -4411,7 +4433,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -4428,7 +4450,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -4445,7 +4467,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -4462,7 +4484,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -4479,7 +4501,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -4496,7 +4518,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -4513,7 +4535,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -4530,7 +4552,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -4547,7 +4569,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -4564,7 +4586,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -4581,7 +4603,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -4598,7 +4620,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -4615,7 +4637,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -4632,7 +4654,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -4649,7 +4671,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -4666,7 +4688,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -4683,7 +4705,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -4700,7 +4722,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -4717,7 +4739,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -4734,7 +4756,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -4751,7 +4773,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -4768,7 +4790,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -4785,7 +4807,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -4802,7 +4824,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -4819,7 +4841,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -4836,7 +4858,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -4853,7 +4875,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -4870,7 +4892,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -4887,7 +4909,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -4904,7 +4926,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -4921,7 +4943,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -4938,7 +4960,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -4955,7 +4977,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -4972,7 +4994,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -4989,7 +5011,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -5006,7 +5028,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -5023,7 +5045,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -5040,7 +5062,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -5057,7 +5079,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -5074,7 +5096,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -5091,7 +5113,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -5108,7 +5130,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -5125,7 +5147,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -5142,7 +5164,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -5159,7 +5181,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -5176,7 +5198,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -5193,7 +5215,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -5210,7 +5232,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -5227,7 +5249,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -5244,7 +5266,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -5261,7 +5283,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -5278,7 +5300,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -5295,7 +5317,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -5312,7 +5334,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -5329,7 +5351,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -5346,7 +5368,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -5363,7 +5385,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -5380,7 +5402,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -5397,7 +5419,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -5414,7 +5436,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -5431,7 +5453,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -5448,7 +5470,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -5465,7 +5487,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -5482,7 +5504,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -5499,7 +5521,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -5516,7 +5538,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -5533,7 +5555,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -5550,7 +5572,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -5567,7 +5589,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>131</v>
       </c>
@@ -5584,7 +5606,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>132</v>
       </c>
